--- a/improvement/manufacturing/plan-02.xlsx
+++ b/improvement/manufacturing/plan-02.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>28名（うち製造現場20名・検査3名）</t>
+          <t>18名（うち製造現場12名・検査2名）</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>新事業進出・ものづくり商業サービス補助金</t>
+          <t>ものづくり・商業・サービス生産性向上促進補助金</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>革新的新製品・サービス枠 750万〜3,500万円（従業員規模により変動）</t>
+          <t>製品・サービス高付加価値化枠。従業員規模により変動（当該公募回の公募要領で確認）</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>ものづくり補助金は機械装置・システム構築費を対象経費とし、賃上げ要件を満たす事業計画が必要（新事業進出・ものづくり補助金 公式）</t>
+          <t>ものづくり・商業・サービス生産性向上促進補助金は機械装置・システム構築費を対象経費とし、給与支給総額や事業場内最低賃金の賃上げ要件を満たす事業計画が必要（同補助金 公募要領）</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr"/>
